--- a/data/main/wnba.xlsx
+++ b/data/main/wnba.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ18" headerRowCount="1">
-  <autoFilter ref="A1:CQ18"/>
-  <tableColumns count="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR19" headerRowCount="1">
+  <autoFilter ref="A1:CR19"/>
+  <tableColumns count="96">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -392,12 +392,13 @@
     <tableColumn id="87" name="unavailable_features"/>
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
-    <tableColumn id="90" name="rest_disparity"/>
-    <tableColumn id="91" name="back_to_back_gap"/>
-    <tableColumn id="92" name="games_last_7_gap"/>
-    <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="market_residual_probability"/>
-    <tableColumn id="95" name="trade_candidate"/>
+    <tableColumn id="90" name="bullpen_weakness_gap"/>
+    <tableColumn id="91" name="rest_disparity"/>
+    <tableColumn id="92" name="back_to_back_gap"/>
+    <tableColumn id="93" name="games_last_7_gap"/>
+    <tableColumn id="94" name="schedule_missingness"/>
+    <tableColumn id="95" name="market_residual_probability"/>
+    <tableColumn id="96" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -754,19 +755,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$18)</f>
+        <f>COUNTA('Picks'!$A$2:$A$19)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$18,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$19,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$19,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")+COUNTIFS('Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +795,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$18,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$19,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")/(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"win")/(COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"win")+COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$18)/SUM('Picks'!$BX$2:$BX$18),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$19)/SUM('Picks'!$BX$2:$BX$19),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +835,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$18)</f>
+        <f>SUM('Picks'!$BY$2:$BY$19)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$18,"&lt;&gt;",'Picks'!$AB$2:$AB$18),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$19,"&lt;&gt;",'Picks'!$AB$2:$AB$19),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$19,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$19,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$18,'Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$19,'Picks'!$AM$2:$AM$19,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +902,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +918,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$19,'Picks'!$H$2:$H$19,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$19,'Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +933,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +949,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$19,'Picks'!$H$2:$H$19,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$19,'Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +964,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +980,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$19,'Picks'!$H$2:$H$19,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$19,'Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ18"/>
+  <dimension ref="A1:CR19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1104,12 +1105,13 @@
     <col width="22" customWidth="1" min="87" max="87"/>
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
-    <col width="16" customWidth="1" min="90" max="90"/>
-    <col width="18" customWidth="1" min="91" max="91"/>
+    <col width="22" customWidth="1" min="90" max="90"/>
+    <col width="16" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
-    <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="93" max="93"/>
     <col width="22" customWidth="1" min="94" max="94"/>
-    <col width="17" customWidth="1" min="95" max="95"/>
+    <col width="22" customWidth="1" min="95" max="95"/>
+    <col width="17" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1560,30 +1562,35 @@
       </c>
       <c r="CL1" s="23" t="inlineStr">
         <is>
+          <t>bullpen_weakness_gap</t>
+        </is>
+      </c>
+      <c r="CM1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CM1" s="23" t="inlineStr">
+      <c r="CN1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1879,6 +1886,7 @@
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
+      <c r="CR2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2166,6 +2174,7 @@
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
+      <c r="CR3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2457,6 +2466,7 @@
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
+      <c r="CR4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2748,6 +2758,7 @@
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
+      <c r="CR5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3039,6 +3050,7 @@
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
+      <c r="CR6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3326,6 +3338,7 @@
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
+      <c r="CR7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3613,6 +3626,7 @@
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
+      <c r="CR8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3904,6 +3918,7 @@
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
+      <c r="CR9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4191,6 +4206,7 @@
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
+      <c r="CR10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4482,6 +4498,7 @@
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
+      <c r="CR11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4771,12 +4788,13 @@
       <c r="CM12" s="24" t="n"/>
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
-      <c r="CP12" s="24" t="inlineStr">
+      <c r="CP12" s="24" t="n"/>
+      <c r="CQ12" s="24" t="inlineStr">
         <is>
           <t>0.643489</t>
         </is>
       </c>
-      <c r="CQ12" s="24" t="inlineStr">
+      <c r="CR12" s="24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5070,12 +5088,13 @@
       <c r="CM13" s="24" t="n"/>
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
-      <c r="CP13" s="24" t="inlineStr">
+      <c r="CP13" s="24" t="n"/>
+      <c r="CQ13" s="24" t="inlineStr">
         <is>
           <t>0.57112</t>
         </is>
       </c>
-      <c r="CQ13" s="24" t="inlineStr">
+      <c r="CR13" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5369,12 +5388,13 @@
       <c r="CM14" s="24" t="n"/>
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
-      <c r="CP14" s="24" t="inlineStr">
+      <c r="CP14" s="24" t="n"/>
+      <c r="CQ14" s="24" t="inlineStr">
         <is>
           <t>0.758559</t>
         </is>
       </c>
-      <c r="CQ14" s="24" t="inlineStr">
+      <c r="CR14" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,12 +5688,13 @@
       <c r="CM15" s="24" t="n"/>
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
-      <c r="CP15" s="24" t="inlineStr">
+      <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="inlineStr">
         <is>
           <t>0.772803</t>
         </is>
       </c>
-      <c r="CQ15" s="24" t="inlineStr">
+      <c r="CR15" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5963,12 +5984,13 @@
       <c r="CM16" s="24" t="n"/>
       <c r="CN16" s="24" t="n"/>
       <c r="CO16" s="24" t="n"/>
-      <c r="CP16" s="24" t="inlineStr">
+      <c r="CP16" s="24" t="n"/>
+      <c r="CQ16" s="24" t="inlineStr">
         <is>
           <t>0.51407</t>
         </is>
       </c>
-      <c r="CQ16" s="24" t="inlineStr">
+      <c r="CR16" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6258,12 +6280,13 @@
       <c r="CM17" s="24" t="n"/>
       <c r="CN17" s="24" t="n"/>
       <c r="CO17" s="24" t="n"/>
-      <c r="CP17" s="24" t="inlineStr">
+      <c r="CP17" s="24" t="n"/>
+      <c r="CQ17" s="24" t="inlineStr">
         <is>
           <t>0.668225</t>
         </is>
       </c>
-      <c r="CQ17" s="24" t="inlineStr">
+      <c r="CR17" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6557,14 +6580,301 @@
       <c r="CM18" s="24" t="n"/>
       <c r="CN18" s="24" t="n"/>
       <c r="CO18" s="24" t="n"/>
-      <c r="CP18" s="24" t="inlineStr">
+      <c r="CP18" s="24" t="n"/>
+      <c r="CQ18" s="24" t="inlineStr">
         <is>
           <t>0.580877</t>
         </is>
       </c>
-      <c r="CQ18" s="24" t="inlineStr">
+      <c r="CR18" s="24" t="inlineStr">
         <is>
           <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>5a496bcc345544b6</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:42.290404Z</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>401857114</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>-733</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>1.136426</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <v>0.879952</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <v>0.774468</v>
+      </c>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="28" t="n">
+        <v>-0.105484</v>
+      </c>
+      <c r="R19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="n"/>
+      <c r="W19" s="26" t="n"/>
+      <c r="X19" s="26" t="n"/>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="26" t="n"/>
+      <c r="AA19" s="28" t="n"/>
+      <c r="AB19" s="28" t="n"/>
+      <c r="AC19" s="30" t="n"/>
+      <c r="AD19" s="24" t="n"/>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.8800 (aec-wnba-tor-gsv-2026-08-04); model edge vs ask -0.1055.</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG19" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN19" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP19" s="24" t="inlineStr">
+        <is>
+          <t>wnba-tor</t>
+        </is>
+      </c>
+      <c r="AQ19" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="AR19" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="AS19" s="24" t="inlineStr">
+        <is>
+          <t>wnba-gsv</t>
+        </is>
+      </c>
+      <c r="AT19" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="AU19" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="AV19" s="24" t="n"/>
+      <c r="AW19" s="24" t="n"/>
+      <c r="AX19" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY19" s="24" t="n"/>
+      <c r="AZ19" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA19" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB19" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC19" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD19" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE19" s="24" t="inlineStr">
+        <is>
+          <t>fb46ae94639bf9af</t>
+        </is>
+      </c>
+      <c r="BF19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG19" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:25.832875Z</t>
+        </is>
+      </c>
+      <c r="BI19" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ19" s="25" t="n"/>
+      <c r="BK19" s="26" t="n">
+        <v>-733</v>
+      </c>
+      <c r="BL19" s="27" t="n">
+        <v>1.136426</v>
+      </c>
+      <c r="BM19" s="28" t="n">
+        <v>0.879952</v>
+      </c>
+      <c r="BN19" s="28" t="n">
+        <v>0.871287</v>
+      </c>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
+      <c r="BR19" s="28" t="n"/>
+      <c r="BS19" s="28" t="n"/>
+      <c r="BT19" s="28" t="n"/>
+      <c r="BU19" s="25" t="n"/>
+      <c r="BV19" s="29" t="n"/>
+      <c r="BW19" s="24" t="n"/>
+      <c r="BX19" s="30" t="n"/>
+      <c r="BY19" s="27" t="n"/>
+      <c r="BZ19" s="24" t="n"/>
+      <c r="CA19" s="31" t="n"/>
+      <c r="CB19" s="24" t="n"/>
+      <c r="CC19" s="24" t="inlineStr">
+        <is>
+          <t>0.9026326565</t>
+        </is>
+      </c>
+      <c r="CD19" s="24" t="inlineStr">
+        <is>
+          <t>2.972439</t>
+        </is>
+      </c>
+      <c r="CE19" s="24" t="n"/>
+      <c r="CF19" s="24" t="n"/>
+      <c r="CG19" s="24" t="n"/>
+      <c r="CH19" s="24" t="n"/>
+      <c r="CI19" s="24" t="n"/>
+      <c r="CJ19" s="24" t="inlineStr">
+        <is>
+          <t>1.230079</t>
+        </is>
+      </c>
+      <c r="CK19" s="24" t="n"/>
+      <c r="CL19" s="24" t="n"/>
+      <c r="CM19" s="24" t="n"/>
+      <c r="CN19" s="24" t="n"/>
+      <c r="CO19" s="24" t="n"/>
+      <c r="CP19" s="24" t="n"/>
+      <c r="CQ19" s="24" t="inlineStr">
+        <is>
+          <t>0.774468</t>
+        </is>
+      </c>
+      <c r="CR19" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>

--- a/data/main/wnba.xlsx
+++ b/data/main/wnba.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR19" headerRowCount="1">
-  <autoFilter ref="A1:CR19"/>
-  <tableColumns count="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS19" headerRowCount="1">
+  <autoFilter ref="A1:CS19"/>
+  <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -393,12 +393,13 @@
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
     <tableColumn id="90" name="bullpen_weakness_gap"/>
-    <tableColumn id="91" name="rest_disparity"/>
-    <tableColumn id="92" name="back_to_back_gap"/>
-    <tableColumn id="93" name="games_last_7_gap"/>
-    <tableColumn id="94" name="schedule_missingness"/>
-    <tableColumn id="95" name="market_residual_probability"/>
-    <tableColumn id="96" name="trade_candidate"/>
+    <tableColumn id="91" name="starter_era_gap"/>
+    <tableColumn id="92" name="rest_disparity"/>
+    <tableColumn id="93" name="back_to_back_gap"/>
+    <tableColumn id="94" name="games_last_7_gap"/>
+    <tableColumn id="95" name="schedule_missingness"/>
+    <tableColumn id="96" name="market_residual_probability"/>
+    <tableColumn id="97" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1013,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CR19"/>
+  <dimension ref="A1:CS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,12 +1107,13 @@
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="16" customWidth="1" min="91" max="91"/>
-    <col width="18" customWidth="1" min="92" max="92"/>
+    <col width="17" customWidth="1" min="91" max="91"/>
+    <col width="16" customWidth="1" min="92" max="92"/>
     <col width="18" customWidth="1" min="93" max="93"/>
-    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
     <col width="22" customWidth="1" min="95" max="95"/>
-    <col width="17" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="96" max="96"/>
+    <col width="17" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1567,30 +1569,35 @@
       </c>
       <c r="CM1" s="23" t="inlineStr">
         <is>
+          <t>starter_era_gap</t>
+        </is>
+      </c>
+      <c r="CN1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CR1" s="23" t="inlineStr">
+      <c r="CS1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1887,6 +1894,7 @@
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
       <c r="CR2" s="24" t="n"/>
+      <c r="CS2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2175,6 +2183,7 @@
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
       <c r="CR3" s="24" t="n"/>
+      <c r="CS3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2467,6 +2476,7 @@
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
       <c r="CR4" s="24" t="n"/>
+      <c r="CS4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2759,6 +2769,7 @@
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
       <c r="CR5" s="24" t="n"/>
+      <c r="CS5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3051,6 +3062,7 @@
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
       <c r="CR6" s="24" t="n"/>
+      <c r="CS6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3339,6 +3351,7 @@
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
       <c r="CR7" s="24" t="n"/>
+      <c r="CS7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3627,6 +3640,7 @@
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
       <c r="CR8" s="24" t="n"/>
+      <c r="CS8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3919,6 +3933,7 @@
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
       <c r="CR9" s="24" t="n"/>
+      <c r="CS9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4207,6 +4222,7 @@
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
       <c r="CR10" s="24" t="n"/>
+      <c r="CS10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4499,6 +4515,7 @@
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
       <c r="CR11" s="24" t="n"/>
+      <c r="CS11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4789,12 +4806,13 @@
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
-      <c r="CQ12" s="24" t="inlineStr">
+      <c r="CQ12" s="24" t="n"/>
+      <c r="CR12" s="24" t="inlineStr">
         <is>
           <t>0.643489</t>
         </is>
       </c>
-      <c r="CR12" s="24" t="inlineStr">
+      <c r="CS12" s="24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5089,12 +5107,13 @@
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
-      <c r="CQ13" s="24" t="inlineStr">
+      <c r="CQ13" s="24" t="n"/>
+      <c r="CR13" s="24" t="inlineStr">
         <is>
           <t>0.57112</t>
         </is>
       </c>
-      <c r="CR13" s="24" t="inlineStr">
+      <c r="CS13" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5389,12 +5408,13 @@
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
-      <c r="CQ14" s="24" t="inlineStr">
+      <c r="CQ14" s="24" t="n"/>
+      <c r="CR14" s="24" t="inlineStr">
         <is>
           <t>0.758559</t>
         </is>
       </c>
-      <c r="CR14" s="24" t="inlineStr">
+      <c r="CS14" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5689,12 +5709,13 @@
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
       <c r="CP15" s="24" t="n"/>
-      <c r="CQ15" s="24" t="inlineStr">
+      <c r="CQ15" s="24" t="n"/>
+      <c r="CR15" s="24" t="inlineStr">
         <is>
           <t>0.772803</t>
         </is>
       </c>
-      <c r="CR15" s="24" t="inlineStr">
+      <c r="CS15" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5985,12 +6006,13 @@
       <c r="CN16" s="24" t="n"/>
       <c r="CO16" s="24" t="n"/>
       <c r="CP16" s="24" t="n"/>
-      <c r="CQ16" s="24" t="inlineStr">
+      <c r="CQ16" s="24" t="n"/>
+      <c r="CR16" s="24" t="inlineStr">
         <is>
           <t>0.51407</t>
         </is>
       </c>
-      <c r="CR16" s="24" t="inlineStr">
+      <c r="CS16" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6281,12 +6303,13 @@
       <c r="CN17" s="24" t="n"/>
       <c r="CO17" s="24" t="n"/>
       <c r="CP17" s="24" t="n"/>
-      <c r="CQ17" s="24" t="inlineStr">
+      <c r="CQ17" s="24" t="n"/>
+      <c r="CR17" s="24" t="inlineStr">
         <is>
           <t>0.668225</t>
         </is>
       </c>
-      <c r="CR17" s="24" t="inlineStr">
+      <c r="CS17" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6581,12 +6604,13 @@
       <c r="CN18" s="24" t="n"/>
       <c r="CO18" s="24" t="n"/>
       <c r="CP18" s="24" t="n"/>
-      <c r="CQ18" s="24" t="inlineStr">
+      <c r="CQ18" s="24" t="n"/>
+      <c r="CR18" s="24" t="inlineStr">
         <is>
           <t>0.580877</t>
         </is>
       </c>
-      <c r="CR18" s="24" t="inlineStr">
+      <c r="CS18" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6595,12 +6619,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>5a496bcc345544b6</t>
+          <t>1142ac42f2254e3c</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:42.290404Z</t>
+          <t>2026-08-04T14:24:46.511596Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -6806,7 +6830,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:25.832875Z</t>
+          <t>2026-08-04T14:23:15.869749Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6867,12 +6891,13 @@
       <c r="CN19" s="24" t="n"/>
       <c r="CO19" s="24" t="n"/>
       <c r="CP19" s="24" t="n"/>
-      <c r="CQ19" s="24" t="inlineStr">
+      <c r="CQ19" s="24" t="n"/>
+      <c r="CR19" s="24" t="inlineStr">
         <is>
           <t>0.774468</t>
         </is>
       </c>
-      <c r="CR19" s="24" t="inlineStr">
+      <c r="CS19" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/data/main/wnba.xlsx
+++ b/data/main/wnba.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS19" headerRowCount="1">
-  <autoFilter ref="A1:CS19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS23" headerRowCount="1">
+  <autoFilter ref="A1:CS23"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$19)</f>
+        <f>COUNTA('Picks'!$A$2:$A$23)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$19,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$23,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$19,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")+COUNTIFS('Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")+COUNTIFS('Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$19,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$23,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"win")/(COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"win")+COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")/(COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")+COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$19)/SUM('Picks'!$BX$2:$BX$19),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$23)/SUM('Picks'!$BX$2:$BX$23),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$19)</f>
+        <f>SUM('Picks'!$BY$2:$BY$23)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$19,"&lt;&gt;",'Picks'!$AB$2:$AB$19),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$23,"&lt;&gt;",'Picks'!$AB$2:$AB$23),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$19,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$19,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$23,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$19,'Picks'!$AM$2:$AM$19,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$23,'Picks'!$AM$2:$AM$23,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$19,'Picks'!$H$2:$H$19,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$19,'Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$19,'Picks'!$H$2:$H$19,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$19,'Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$19,'Picks'!$H$2:$H$19,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$19,'Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS19"/>
+  <dimension ref="A1:CS23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6619,12 +6619,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>1142ac42f2254e3c</t>
+          <t>b168d7d686c645e1</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:24:46.511596Z</t>
+          <t>2026-08-05T01:07:48.070985Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -6669,20 +6669,20 @@
         </is>
       </c>
       <c r="L19" s="26" t="n">
-        <v>-733</v>
+        <v>-614</v>
       </c>
       <c r="M19" s="27" t="n">
-        <v>1.136426</v>
+        <v>1.162866</v>
       </c>
       <c r="N19" s="28" t="n">
-        <v>0.879952</v>
+        <v>0.859944</v>
       </c>
       <c r="O19" s="28" t="n">
         <v>0.774468</v>
       </c>
       <c r="P19" s="28" t="n"/>
       <c r="Q19" s="28" t="n">
-        <v>-0.105484</v>
+        <v>-0.085476</v>
       </c>
       <c r="R19" s="26" t="n">
         <v>0</v>
@@ -6697,21 +6697,35 @@
       </c>
       <c r="U19" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V19" s="24" t="n"/>
-      <c r="W19" s="26" t="n"/>
-      <c r="X19" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <v>92</v>
+      </c>
       <c r="Y19" s="25" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n"/>
-      <c r="AD19" s="24" t="n"/>
+      <c r="AC19" s="30" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:21:25.381491Z</t>
+        </is>
+      </c>
       <c r="AE19" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.8800 (aec-wnba-tor-gsv-2026-08-04); model edge vs ask -0.1055.</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.8600 (aec-wnba-tor-gsv-2026-08-04); model edge vs ask -0.0855.</t>
         </is>
       </c>
       <c r="AF19" s="31" t="inlineStr">
@@ -6830,7 +6844,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:23:15.869749Z</t>
+          <t>2026-08-05T01:07:13.594446Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6840,16 +6854,16 @@
       </c>
       <c r="BJ19" s="25" t="n"/>
       <c r="BK19" s="26" t="n">
-        <v>-733</v>
+        <v>-614</v>
       </c>
       <c r="BL19" s="27" t="n">
-        <v>1.136426</v>
+        <v>1.162866</v>
       </c>
       <c r="BM19" s="28" t="n">
-        <v>0.879952</v>
+        <v>0.859944</v>
       </c>
       <c r="BN19" s="28" t="n">
-        <v>0.871287</v>
+        <v>0.851485</v>
       </c>
       <c r="BO19" s="28" t="n"/>
       <c r="BP19" s="25" t="n"/>
@@ -6903,6 +6917,1162 @@
         </is>
       </c>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>864e1560b09146af</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:35:50.664769Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>401857115</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.660664</v>
+      </c>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="28" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>24</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="n"/>
+      <c r="W20" s="26" t="n"/>
+      <c r="X20" s="26" t="n"/>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n"/>
+      <c r="AA20" s="28" t="n"/>
+      <c r="AB20" s="28" t="n"/>
+      <c r="AC20" s="30" t="n"/>
+      <c r="AD20" s="24" t="n"/>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.6600 (aec-wnba-phx-atl-2026-08-05); model edge vs ask +0.0007.</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>wnba-phx</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>wnba-atl</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>db4cf2e6209fa446</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:03.119408Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN20" s="28" t="n">
+        <v>0.653465</v>
+      </c>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
+      <c r="BR20" s="28" t="n"/>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="inlineStr">
+        <is>
+          <t>0.708542691</t>
+        </is>
+      </c>
+      <c r="CD20" s="24" t="inlineStr">
+        <is>
+          <t>-1.788883</t>
+        </is>
+      </c>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="inlineStr">
+        <is>
+          <t>-1.7391</t>
+        </is>
+      </c>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+      <c r="CP20" s="24" t="n"/>
+      <c r="CQ20" s="24" t="n"/>
+      <c r="CR20" s="24" t="inlineStr">
+        <is>
+          <t>0.660664</t>
+        </is>
+      </c>
+      <c r="CS20" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>0567d22e81a84780</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:35:50.664769Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>401857116</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>-376</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>1.265957</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.789916</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.741322</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>-0.048594</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="n"/>
+      <c r="W21" s="26" t="n"/>
+      <c r="X21" s="26" t="n"/>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n"/>
+      <c r="AD21" s="24" t="n"/>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.7900 (aec-wnba-sea-ny-2026-08-05); model edge vs ask -0.0487.</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>wnba-sea</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>wnba-nyl</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>cbc087f3d2f12e27</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:04.100169Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>-376</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>1.265957</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.789916</v>
+      </c>
+      <c r="BN21" s="28" t="n">
+        <v>0.782178</v>
+      </c>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="inlineStr">
+        <is>
+          <t>0.8394756417</t>
+        </is>
+      </c>
+      <c r="CD21" s="24" t="inlineStr">
+        <is>
+          <t>0.315883</t>
+        </is>
+      </c>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="inlineStr">
+        <is>
+          <t>1.520421</t>
+        </is>
+      </c>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="n"/>
+      <c r="CR21" s="24" t="inlineStr">
+        <is>
+          <t>0.741322</t>
+        </is>
+      </c>
+      <c r="CS21" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>e1dad84c760945eb</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:35:50.664769Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>401857117</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.532764</v>
+      </c>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n">
+        <v>-0.0574</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="n"/>
+      <c r="W22" s="26" t="n"/>
+      <c r="X22" s="26" t="n"/>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n"/>
+      <c r="AD22" s="24" t="n"/>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5900 (aec-wnba-dal-wsh-2026-08-05); model edge vs ask -0.0572. NOTE: NO_CALL_AVAILABILITY_REPORT_INCOMPLETE unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>wnba-dal</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>wnba-was</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>72f5694b0619f905</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:04.826877Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN22" s="28" t="n">
+        <v>0.584158</v>
+      </c>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="inlineStr">
+        <is>
+          <t>0.4611418469</t>
+        </is>
+      </c>
+      <c r="CD22" s="24" t="inlineStr">
+        <is>
+          <t>1.287558</t>
+        </is>
+      </c>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_REPORT_INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="CJ22" s="24" t="inlineStr">
+        <is>
+          <t>-1.305803</t>
+        </is>
+      </c>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="inlineStr">
+        <is>
+          <t>0.532764</t>
+        </is>
+      </c>
+      <c r="CS22" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>36a1fc4448e649ce</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:35:50.664769Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>401857118</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.549529</v>
+      </c>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="28" t="n">
+        <v>-0.009941999999999999</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="n"/>
+      <c r="W23" s="26" t="n"/>
+      <c r="X23" s="26" t="n"/>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n"/>
+      <c r="AD23" s="24" t="n"/>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5600 (aec-wnba-la-chi-2026-08-05); model edge vs ask -0.0105. NOTE: NO_CALL_AVAILABILITY_REPORT_INCOMPLETE unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>wnba-las</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>wnba-chi</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>5cc21b269728431d</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:05.642651Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN23" s="28" t="n">
+        <v>0.554455</v>
+      </c>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="inlineStr">
+        <is>
+          <t>0.573492291</t>
+        </is>
+      </c>
+      <c r="CD23" s="24" t="inlineStr">
+        <is>
+          <t>3.024749</t>
+        </is>
+      </c>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_REPORT_INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="CJ23" s="24" t="inlineStr">
+        <is>
+          <t>2.235061</t>
+        </is>
+      </c>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="inlineStr">
+        <is>
+          <t>0.549529</t>
+        </is>
+      </c>
+      <c r="CS23" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/main/wnba.xlsx
+++ b/data/main/wnba.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -6920,12 +6920,12 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>864e1560b09146af</t>
+          <t>44cbe8b8d0264820</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:03.119408Z</t>
+          <t>2026-08-05T13:52:33.816980Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -7207,12 +7207,12 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>0567d22e81a84780</t>
+          <t>00b48726a83d4197</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -7257,23 +7257,23 @@
         </is>
       </c>
       <c r="L21" s="26" t="n">
-        <v>-376</v>
+        <v>-335</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>1.265957</v>
+        <v>1.298507</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.789916</v>
+        <v>0.770115</v>
       </c>
       <c r="O21" s="28" t="n">
         <v>0.741322</v>
       </c>
       <c r="P21" s="28" t="n"/>
       <c r="Q21" s="28" t="n">
-        <v>-0.048594</v>
+        <v>-0.028793</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S21" s="29" t="n">
         <v>2</v>
@@ -7299,7 +7299,7 @@
       <c r="AD21" s="24" t="n"/>
       <c r="AE21" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.7900 (aec-wnba-sea-ny-2026-08-05); model edge vs ask -0.0487.</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.7700 (aec-wnba-sea-ny-2026-08-05); model edge vs ask -0.0287.</t>
         </is>
       </c>
       <c r="AF21" s="31" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:04.100169Z</t>
+          <t>2026-08-05T13:52:34.422318Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7428,16 +7428,16 @@
       </c>
       <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
-        <v>-376</v>
+        <v>-335</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>1.265957</v>
+        <v>1.298507</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.789916</v>
+        <v>0.770115</v>
       </c>
       <c r="BN21" s="28" t="n">
-        <v>0.782178</v>
+        <v>0.7623760000000001</v>
       </c>
       <c r="BO21" s="28" t="n"/>
       <c r="BP21" s="25" t="n"/>
@@ -7494,12 +7494,12 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>e1dad84c760945eb</t>
+          <t>9c65544ccda74f54</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -7544,23 +7544,23 @@
         </is>
       </c>
       <c r="L22" s="26" t="n">
-        <v>-144</v>
+        <v>-133</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.75188</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.570815</v>
       </c>
       <c r="O22" s="28" t="n">
         <v>0.532764</v>
       </c>
       <c r="P22" s="28" t="n"/>
       <c r="Q22" s="28" t="n">
-        <v>-0.0574</v>
+        <v>-0.038051</v>
       </c>
       <c r="R22" s="26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S22" s="29" t="n">
         <v>1</v>
@@ -7586,7 +7586,7 @@
       <c r="AD22" s="24" t="n"/>
       <c r="AE22" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.5900 (aec-wnba-dal-wsh-2026-08-05); model edge vs ask -0.0572. NOTE: NO_CALL_AVAILABILITY_REPORT_INCOMPLETE unavailable for this game — defaulted to neutral, other features used normally.</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5700 (aec-wnba-dal-wsh-2026-08-05); model edge vs ask -0.0372. NOTE: NO_CALL_AVAILABILITY_REPORT_INCOMPLETE unavailable for this game — defaulted to neutral, other features used normally.</t>
         </is>
       </c>
       <c r="AF22" s="31" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:04.826877Z</t>
+          <t>2026-08-05T13:52:34.867255Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7715,16 +7715,16 @@
       </c>
       <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
-        <v>-144</v>
+        <v>-133</v>
       </c>
       <c r="BL22" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.75188</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.570815</v>
       </c>
       <c r="BN22" s="28" t="n">
-        <v>0.584158</v>
+        <v>0.564356</v>
       </c>
       <c r="BO22" s="28" t="n"/>
       <c r="BP22" s="25" t="n"/>
@@ -7785,12 +7785,12 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>36a1fc4448e649ce</t>
+          <t>574a844222a04524</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -7835,23 +7835,23 @@
         </is>
       </c>
       <c r="L23" s="26" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="M23" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.75188</v>
       </c>
       <c r="N23" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.570815</v>
       </c>
       <c r="O23" s="28" t="n">
         <v>0.549529</v>
       </c>
       <c r="P23" s="28" t="n"/>
       <c r="Q23" s="28" t="n">
-        <v>-0.009941999999999999</v>
+        <v>-0.021286</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="S23" s="29" t="n">
         <v>1</v>
@@ -7877,7 +7877,7 @@
       <c r="AD23" s="24" t="n"/>
       <c r="AE23" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.5600 (aec-wnba-la-chi-2026-08-05); model edge vs ask -0.0105. NOTE: NO_CALL_AVAILABILITY_REPORT_INCOMPLETE unavailable for this game — defaulted to neutral, other features used normally.</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5700 (aec-wnba-la-chi-2026-08-05); model edge vs ask -0.0205. NOTE: NO_CALL_AVAILABILITY_REPORT_INCOMPLETE unavailable for this game — defaulted to neutral, other features used normally.</t>
         </is>
       </c>
       <c r="AF23" s="31" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:05.642651Z</t>
+          <t>2026-08-05T13:52:35.451044Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -8006,16 +8006,16 @@
       </c>
       <c r="BJ23" s="25" t="n"/>
       <c r="BK23" s="26" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="BL23" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.75188</v>
       </c>
       <c r="BM23" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.570815</v>
       </c>
       <c r="BN23" s="28" t="n">
-        <v>0.554455</v>
+        <v>0.564356</v>
       </c>
       <c r="BO23" s="28" t="n"/>
       <c r="BP23" s="25" t="n"/>

--- a/data/main/wnba.xlsx
+++ b/data/main/wnba.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS23" headerRowCount="1">
-  <autoFilter ref="A1:CS23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS20" headerRowCount="1">
+  <autoFilter ref="A1:CS20"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$23)</f>
+        <f>COUNTA('Picks'!$A$2:$A$20)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$23,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$20,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")+COUNTIFS('Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")+COUNTIFS('Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$23,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$20,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")/(COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")+COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")/(COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")+COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$23)/SUM('Picks'!$BX$2:$BX$23),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$20)/SUM('Picks'!$BX$2:$BX$20),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$23)</f>
+        <f>SUM('Picks'!$BY$2:$BY$20)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$23,"&lt;&gt;",'Picks'!$AB$2:$AB$23),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$20,"&lt;&gt;",'Picks'!$AB$2:$AB$20),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$23,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$20,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$23,'Picks'!$AM$2:$AM$23,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$20,'Picks'!$AM$2:$AM$20,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS23"/>
+  <dimension ref="A1:CS20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6920,22 +6920,22 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>44cbe8b8d0264820</t>
+          <t>1bfd472cf4414d5e</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:54:09.180176Z</t>
+          <t>2026-08-07T15:21:40.990328Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T19:00:00-0400</t>
+          <t>2026-08-07T19:30:00-0400</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>401857115</t>
+          <t>401857123</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>Phoenix Mercury</t>
+          <t>Atlanta Dream</t>
         </is>
       </c>
       <c r="G20" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Dream</t>
+          <t>Washington Mystics</t>
         </is>
       </c>
       <c r="H20" s="24" t="inlineStr">
@@ -6970,26 +6970,26 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>-194</v>
+        <v>194</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>1.515464</v>
+        <v>2.94</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.340136</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>0.660664</v>
+        <v>0.561972</v>
       </c>
       <c r="P20" s="28" t="n"/>
       <c r="Q20" s="28" t="n">
-        <v>0.0008</v>
+        <v>0.221836</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="S20" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T20" s="24" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
       <c r="AD20" s="24" t="n"/>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.6600 (aec-wnba-phx-atl-2026-08-05); model edge vs ask +0.0007.</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.3400 (aec-wnba-atl-wsh-2026-08-07); model edge vs ask +0.2220.</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -7053,32 +7053,32 @@
       </c>
       <c r="AP20" s="24" t="inlineStr">
         <is>
-          <t>wnba-phx</t>
+          <t>wnba-atl</t>
         </is>
       </c>
       <c r="AQ20" s="24" t="inlineStr">
         <is>
-          <t>Phoenix Mercury</t>
+          <t>Atlanta Dream</t>
         </is>
       </c>
       <c r="AR20" s="24" t="inlineStr">
         <is>
-          <t>Phoenix Mercury</t>
+          <t>Atlanta Dream</t>
         </is>
       </c>
       <c r="AS20" s="24" t="inlineStr">
         <is>
-          <t>wnba-atl</t>
+          <t>wnba-was</t>
         </is>
       </c>
       <c r="AT20" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Dream</t>
+          <t>Washington Mystics</t>
         </is>
       </c>
       <c r="AU20" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Dream</t>
+          <t>Washington Mystics</t>
         </is>
       </c>
       <c r="AV20" s="24" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="BE20" s="24" t="inlineStr">
         <is>
-          <t>db4cf2e6209fa446</t>
+          <t>7527e38cbf3d298e</t>
         </is>
       </c>
       <c r="BF20" s="24" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:52:33.816980Z</t>
+          <t>2026-08-07T15:20:39.610102Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -7141,16 +7141,16 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>-194</v>
+        <v>194</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>1.515464</v>
+        <v>2.94</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.340136</v>
       </c>
       <c r="BN20" s="28" t="n">
-        <v>0.653465</v>
+        <v>0.336634</v>
       </c>
       <c r="BO20" s="28" t="n"/>
       <c r="BP20" s="25" t="n"/>
@@ -7168,12 +7168,12 @@
       <c r="CB20" s="24" t="n"/>
       <c r="CC20" s="24" t="inlineStr">
         <is>
-          <t>0.708542691</t>
+          <t>0.5839932663</t>
         </is>
       </c>
       <c r="CD20" s="24" t="inlineStr">
         <is>
-          <t>-1.788883</t>
+          <t>-1.592597</t>
         </is>
       </c>
       <c r="CE20" s="24" t="n"/>
@@ -7183,7 +7183,7 @@
       <c r="CI20" s="24" t="n"/>
       <c r="CJ20" s="24" t="inlineStr">
         <is>
-          <t>-1.7391</t>
+          <t>6.900454</t>
         </is>
       </c>
       <c r="CK20" s="24" t="n"/>
@@ -7195,881 +7195,12 @@
       <c r="CQ20" s="24" t="n"/>
       <c r="CR20" s="24" t="inlineStr">
         <is>
-          <t>0.660664</t>
+          <t>0.561972</t>
         </is>
       </c>
       <c r="CS20" s="24" t="inlineStr">
         <is>
           <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
-        <is>
-          <t>00b48726a83d4197</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:09.180176Z</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T19:00:00-0400</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>401857116</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
-        <is>
-          <t>WNBA</t>
-        </is>
-      </c>
-      <c r="F21" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Storm</t>
-        </is>
-      </c>
-      <c r="G21" s="24" t="inlineStr">
-        <is>
-          <t>New York Liberty</t>
-        </is>
-      </c>
-      <c r="H21" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I21" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J21" s="25" t="n"/>
-      <c r="K21" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L21" s="26" t="n">
-        <v>-335</v>
-      </c>
-      <c r="M21" s="27" t="n">
-        <v>1.298507</v>
-      </c>
-      <c r="N21" s="28" t="n">
-        <v>0.770115</v>
-      </c>
-      <c r="O21" s="28" t="n">
-        <v>0.741322</v>
-      </c>
-      <c r="P21" s="28" t="n"/>
-      <c r="Q21" s="28" t="n">
-        <v>-0.028793</v>
-      </c>
-      <c r="R21" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="S21" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="U21" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V21" s="24" t="n"/>
-      <c r="W21" s="26" t="n"/>
-      <c r="X21" s="26" t="n"/>
-      <c r="Y21" s="25" t="n"/>
-      <c r="Z21" s="26" t="n"/>
-      <c r="AA21" s="28" t="n"/>
-      <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n"/>
-      <c r="AD21" s="24" t="n"/>
-      <c r="AE21" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.7700 (aec-wnba-sea-ny-2026-08-05); model edge vs ask -0.0287.</t>
-        </is>
-      </c>
-      <c r="AF21" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; shadow-qualified via operator override.</t>
-        </is>
-      </c>
-      <c r="AG21" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH21" s="24" t="n"/>
-      <c r="AI21" s="31" t="n"/>
-      <c r="AJ21" s="31" t="n"/>
-      <c r="AK21" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL21" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM21" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN21" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO21" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP21" s="24" t="inlineStr">
-        <is>
-          <t>wnba-sea</t>
-        </is>
-      </c>
-      <c r="AQ21" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Storm</t>
-        </is>
-      </c>
-      <c r="AR21" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Storm</t>
-        </is>
-      </c>
-      <c r="AS21" s="24" t="inlineStr">
-        <is>
-          <t>wnba-nyl</t>
-        </is>
-      </c>
-      <c r="AT21" s="24" t="inlineStr">
-        <is>
-          <t>New York Liberty</t>
-        </is>
-      </c>
-      <c r="AU21" s="24" t="inlineStr">
-        <is>
-          <t>New York Liberty</t>
-        </is>
-      </c>
-      <c r="AV21" s="24" t="n"/>
-      <c r="AW21" s="24" t="n"/>
-      <c r="AX21" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY21" s="24" t="n"/>
-      <c r="AZ21" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA21" s="24" t="inlineStr">
-        <is>
-          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
-        </is>
-      </c>
-      <c r="BB21" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC21" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BD21" s="24" t="inlineStr">
-        <is>
-          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
-        </is>
-      </c>
-      <c r="BE21" s="24" t="inlineStr">
-        <is>
-          <t>cbc087f3d2f12e27</t>
-        </is>
-      </c>
-      <c r="BF21" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG21" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BH21" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:52:34.422318Z</t>
-        </is>
-      </c>
-      <c r="BI21" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ21" s="25" t="n"/>
-      <c r="BK21" s="26" t="n">
-        <v>-335</v>
-      </c>
-      <c r="BL21" s="27" t="n">
-        <v>1.298507</v>
-      </c>
-      <c r="BM21" s="28" t="n">
-        <v>0.770115</v>
-      </c>
-      <c r="BN21" s="28" t="n">
-        <v>0.7623760000000001</v>
-      </c>
-      <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n"/>
-      <c r="BR21" s="28" t="n"/>
-      <c r="BS21" s="28" t="n"/>
-      <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="25" t="n"/>
-      <c r="BV21" s="29" t="n"/>
-      <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="30" t="n"/>
-      <c r="BY21" s="27" t="n"/>
-      <c r="BZ21" s="24" t="n"/>
-      <c r="CA21" s="31" t="n"/>
-      <c r="CB21" s="24" t="n"/>
-      <c r="CC21" s="24" t="inlineStr">
-        <is>
-          <t>0.8394756417</t>
-        </is>
-      </c>
-      <c r="CD21" s="24" t="inlineStr">
-        <is>
-          <t>0.315883</t>
-        </is>
-      </c>
-      <c r="CE21" s="24" t="n"/>
-      <c r="CF21" s="24" t="n"/>
-      <c r="CG21" s="24" t="n"/>
-      <c r="CH21" s="24" t="n"/>
-      <c r="CI21" s="24" t="n"/>
-      <c r="CJ21" s="24" t="inlineStr">
-        <is>
-          <t>1.520421</t>
-        </is>
-      </c>
-      <c r="CK21" s="24" t="n"/>
-      <c r="CL21" s="24" t="n"/>
-      <c r="CM21" s="24" t="n"/>
-      <c r="CN21" s="24" t="n"/>
-      <c r="CO21" s="24" t="n"/>
-      <c r="CP21" s="24" t="n"/>
-      <c r="CQ21" s="24" t="n"/>
-      <c r="CR21" s="24" t="inlineStr">
-        <is>
-          <t>0.741322</t>
-        </is>
-      </c>
-      <c r="CS21" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
-        <is>
-          <t>9c65544ccda74f54</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:09.180176Z</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T19:30:00-0400</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>401857117</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
-        <is>
-          <t>WNBA</t>
-        </is>
-      </c>
-      <c r="F22" s="24" t="inlineStr">
-        <is>
-          <t>Dallas Wings</t>
-        </is>
-      </c>
-      <c r="G22" s="24" t="inlineStr">
-        <is>
-          <t>Washington Mystics</t>
-        </is>
-      </c>
-      <c r="H22" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I22" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J22" s="25" t="n"/>
-      <c r="K22" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L22" s="26" t="n">
-        <v>-133</v>
-      </c>
-      <c r="M22" s="27" t="n">
-        <v>1.75188</v>
-      </c>
-      <c r="N22" s="28" t="n">
-        <v>0.570815</v>
-      </c>
-      <c r="O22" s="28" t="n">
-        <v>0.532764</v>
-      </c>
-      <c r="P22" s="28" t="n"/>
-      <c r="Q22" s="28" t="n">
-        <v>-0.038051</v>
-      </c>
-      <c r="R22" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="S22" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="U22" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V22" s="24" t="n"/>
-      <c r="W22" s="26" t="n"/>
-      <c r="X22" s="26" t="n"/>
-      <c r="Y22" s="25" t="n"/>
-      <c r="Z22" s="26" t="n"/>
-      <c r="AA22" s="28" t="n"/>
-      <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="30" t="n"/>
-      <c r="AD22" s="24" t="n"/>
-      <c r="AE22" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.5700 (aec-wnba-dal-wsh-2026-08-05); model edge vs ask -0.0372. NOTE: NO_CALL_AVAILABILITY_REPORT_INCOMPLETE unavailable for this game — defaulted to neutral, other features used normally.</t>
-        </is>
-      </c>
-      <c r="AF22" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; shadow-qualified via operator override.</t>
-        </is>
-      </c>
-      <c r="AG22" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH22" s="24" t="n"/>
-      <c r="AI22" s="31" t="n"/>
-      <c r="AJ22" s="31" t="n"/>
-      <c r="AK22" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL22" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM22" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN22" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO22" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP22" s="24" t="inlineStr">
-        <is>
-          <t>wnba-dal</t>
-        </is>
-      </c>
-      <c r="AQ22" s="24" t="inlineStr">
-        <is>
-          <t>Dallas Wings</t>
-        </is>
-      </c>
-      <c r="AR22" s="24" t="inlineStr">
-        <is>
-          <t>Dallas Wings</t>
-        </is>
-      </c>
-      <c r="AS22" s="24" t="inlineStr">
-        <is>
-          <t>wnba-was</t>
-        </is>
-      </c>
-      <c r="AT22" s="24" t="inlineStr">
-        <is>
-          <t>Washington Mystics</t>
-        </is>
-      </c>
-      <c r="AU22" s="24" t="inlineStr">
-        <is>
-          <t>Washington Mystics</t>
-        </is>
-      </c>
-      <c r="AV22" s="24" t="n"/>
-      <c r="AW22" s="24" t="n"/>
-      <c r="AX22" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY22" s="24" t="n"/>
-      <c r="AZ22" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA22" s="24" t="inlineStr">
-        <is>
-          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
-        </is>
-      </c>
-      <c r="BB22" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC22" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BD22" s="24" t="inlineStr">
-        <is>
-          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
-        </is>
-      </c>
-      <c r="BE22" s="24" t="inlineStr">
-        <is>
-          <t>72f5694b0619f905</t>
-        </is>
-      </c>
-      <c r="BF22" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG22" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BH22" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:52:34.867255Z</t>
-        </is>
-      </c>
-      <c r="BI22" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ22" s="25" t="n"/>
-      <c r="BK22" s="26" t="n">
-        <v>-133</v>
-      </c>
-      <c r="BL22" s="27" t="n">
-        <v>1.75188</v>
-      </c>
-      <c r="BM22" s="28" t="n">
-        <v>0.570815</v>
-      </c>
-      <c r="BN22" s="28" t="n">
-        <v>0.564356</v>
-      </c>
-      <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="25" t="n"/>
-      <c r="BQ22" s="27" t="n"/>
-      <c r="BR22" s="28" t="n"/>
-      <c r="BS22" s="28" t="n"/>
-      <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="25" t="n"/>
-      <c r="BV22" s="29" t="n"/>
-      <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="30" t="n"/>
-      <c r="BY22" s="27" t="n"/>
-      <c r="BZ22" s="24" t="n"/>
-      <c r="CA22" s="31" t="n"/>
-      <c r="CB22" s="24" t="n"/>
-      <c r="CC22" s="24" t="inlineStr">
-        <is>
-          <t>0.4611418469</t>
-        </is>
-      </c>
-      <c r="CD22" s="24" t="inlineStr">
-        <is>
-          <t>1.287558</t>
-        </is>
-      </c>
-      <c r="CE22" s="24" t="n"/>
-      <c r="CF22" s="24" t="n"/>
-      <c r="CG22" s="24" t="n"/>
-      <c r="CH22" s="24" t="n"/>
-      <c r="CI22" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_AVAILABILITY_REPORT_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="CJ22" s="24" t="inlineStr">
-        <is>
-          <t>-1.305803</t>
-        </is>
-      </c>
-      <c r="CK22" s="24" t="n"/>
-      <c r="CL22" s="24" t="n"/>
-      <c r="CM22" s="24" t="n"/>
-      <c r="CN22" s="24" t="n"/>
-      <c r="CO22" s="24" t="n"/>
-      <c r="CP22" s="24" t="n"/>
-      <c r="CQ22" s="24" t="n"/>
-      <c r="CR22" s="24" t="inlineStr">
-        <is>
-          <t>0.532764</t>
-        </is>
-      </c>
-      <c r="CS22" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="24" t="inlineStr">
-        <is>
-          <t>574a844222a04524</t>
-        </is>
-      </c>
-      <c r="B23" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:09.180176Z</t>
-        </is>
-      </c>
-      <c r="C23" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T21:00:00-0400</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
-        <is>
-          <t>401857118</t>
-        </is>
-      </c>
-      <c r="E23" s="24" t="inlineStr">
-        <is>
-          <t>WNBA</t>
-        </is>
-      </c>
-      <c r="F23" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks</t>
-        </is>
-      </c>
-      <c r="G23" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Sky</t>
-        </is>
-      </c>
-      <c r="H23" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I23" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J23" s="25" t="n"/>
-      <c r="K23" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L23" s="26" t="n">
-        <v>-133</v>
-      </c>
-      <c r="M23" s="27" t="n">
-        <v>1.75188</v>
-      </c>
-      <c r="N23" s="28" t="n">
-        <v>0.570815</v>
-      </c>
-      <c r="O23" s="28" t="n">
-        <v>0.549529</v>
-      </c>
-      <c r="P23" s="28" t="n"/>
-      <c r="Q23" s="28" t="n">
-        <v>-0.021286</v>
-      </c>
-      <c r="R23" s="26" t="n">
-        <v>13</v>
-      </c>
-      <c r="S23" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="U23" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V23" s="24" t="n"/>
-      <c r="W23" s="26" t="n"/>
-      <c r="X23" s="26" t="n"/>
-      <c r="Y23" s="25" t="n"/>
-      <c r="Z23" s="26" t="n"/>
-      <c r="AA23" s="28" t="n"/>
-      <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="30" t="n"/>
-      <c r="AD23" s="24" t="n"/>
-      <c r="AE23" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.5700 (aec-wnba-la-chi-2026-08-05); model edge vs ask -0.0205. NOTE: NO_CALL_AVAILABILITY_REPORT_INCOMPLETE unavailable for this game — defaulted to neutral, other features used normally.</t>
-        </is>
-      </c>
-      <c r="AF23" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; shadow-qualified via operator override.</t>
-        </is>
-      </c>
-      <c r="AG23" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH23" s="24" t="n"/>
-      <c r="AI23" s="31" t="n"/>
-      <c r="AJ23" s="31" t="n"/>
-      <c r="AK23" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL23" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM23" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN23" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO23" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP23" s="24" t="inlineStr">
-        <is>
-          <t>wnba-las</t>
-        </is>
-      </c>
-      <c r="AQ23" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks</t>
-        </is>
-      </c>
-      <c r="AR23" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks</t>
-        </is>
-      </c>
-      <c r="AS23" s="24" t="inlineStr">
-        <is>
-          <t>wnba-chi</t>
-        </is>
-      </c>
-      <c r="AT23" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Sky</t>
-        </is>
-      </c>
-      <c r="AU23" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Sky</t>
-        </is>
-      </c>
-      <c r="AV23" s="24" t="n"/>
-      <c r="AW23" s="24" t="n"/>
-      <c r="AX23" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY23" s="24" t="n"/>
-      <c r="AZ23" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA23" s="24" t="inlineStr">
-        <is>
-          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
-        </is>
-      </c>
-      <c r="BB23" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC23" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BD23" s="24" t="inlineStr">
-        <is>
-          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
-        </is>
-      </c>
-      <c r="BE23" s="24" t="inlineStr">
-        <is>
-          <t>5cc21b269728431d</t>
-        </is>
-      </c>
-      <c r="BF23" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG23" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BH23" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:52:35.451044Z</t>
-        </is>
-      </c>
-      <c r="BI23" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ23" s="25" t="n"/>
-      <c r="BK23" s="26" t="n">
-        <v>-133</v>
-      </c>
-      <c r="BL23" s="27" t="n">
-        <v>1.75188</v>
-      </c>
-      <c r="BM23" s="28" t="n">
-        <v>0.570815</v>
-      </c>
-      <c r="BN23" s="28" t="n">
-        <v>0.564356</v>
-      </c>
-      <c r="BO23" s="28" t="n"/>
-      <c r="BP23" s="25" t="n"/>
-      <c r="BQ23" s="27" t="n"/>
-      <c r="BR23" s="28" t="n"/>
-      <c r="BS23" s="28" t="n"/>
-      <c r="BT23" s="28" t="n"/>
-      <c r="BU23" s="25" t="n"/>
-      <c r="BV23" s="29" t="n"/>
-      <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="30" t="n"/>
-      <c r="BY23" s="27" t="n"/>
-      <c r="BZ23" s="24" t="n"/>
-      <c r="CA23" s="31" t="n"/>
-      <c r="CB23" s="24" t="n"/>
-      <c r="CC23" s="24" t="inlineStr">
-        <is>
-          <t>0.573492291</t>
-        </is>
-      </c>
-      <c r="CD23" s="24" t="inlineStr">
-        <is>
-          <t>3.024749</t>
-        </is>
-      </c>
-      <c r="CE23" s="24" t="n"/>
-      <c r="CF23" s="24" t="n"/>
-      <c r="CG23" s="24" t="n"/>
-      <c r="CH23" s="24" t="n"/>
-      <c r="CI23" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_AVAILABILITY_REPORT_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="CJ23" s="24" t="inlineStr">
-        <is>
-          <t>2.235061</t>
-        </is>
-      </c>
-      <c r="CK23" s="24" t="n"/>
-      <c r="CL23" s="24" t="n"/>
-      <c r="CM23" s="24" t="n"/>
-      <c r="CN23" s="24" t="n"/>
-      <c r="CO23" s="24" t="n"/>
-      <c r="CP23" s="24" t="n"/>
-      <c r="CQ23" s="24" t="n"/>
-      <c r="CR23" s="24" t="inlineStr">
-        <is>
-          <t>0.549529</t>
-        </is>
-      </c>
-      <c r="CS23" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
         </is>
       </c>
     </row>

--- a/data/main/wnba.xlsx
+++ b/data/main/wnba.xlsx
@@ -6920,12 +6920,12 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>1bfd472cf4414d5e</t>
+          <t>495d3d321ad04714</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:21:40.990328Z</t>
+          <t>2026-08-07T18:28:49.432084Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:39.610102Z</t>
+          <t>2026-08-07T18:28:03.051036Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">

--- a/data/main/wnba.xlsx
+++ b/data/main/wnba.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS26" headerRowCount="1">
-  <autoFilter ref="A1:CS26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS29" headerRowCount="1">
+  <autoFilter ref="A1:CS29"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$26)</f>
+        <f>COUNTA('Picks'!$A$2:$A$29)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$26,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$29,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$26,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")+COUNTIFS('Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$26,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$29,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")/(COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")+COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")/(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$26)/SUM('Picks'!$BX$2:$BX$26),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$29)/SUM('Picks'!$BX$2:$BX$29),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$26)</f>
+        <f>SUM('Picks'!$BY$2:$BY$29)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$26,"&lt;&gt;",'Picks'!$AB$2:$AB$26),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$29,"&lt;&gt;",'Picks'!$AB$2:$AB$29),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$26,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$26,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$26,'Picks'!$AM$2:$AM$26,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$29,'Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS26"/>
+  <dimension ref="A1:CS29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9016,6 +9016,875 @@
         </is>
       </c>
     </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>9397e6d8aee7453d</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T19:33:32.932123Z</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T20:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>401857137</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>-426</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>1.234742</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>0.809886</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <v>0.752207</v>
+      </c>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="28" t="n">
+        <v>-0.057679</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="n"/>
+      <c r="W27" s="26" t="n"/>
+      <c r="X27" s="26" t="n"/>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="26" t="n"/>
+      <c r="AA27" s="28" t="n"/>
+      <c r="AB27" s="28" t="n"/>
+      <c r="AC27" s="30" t="n"/>
+      <c r="AD27" s="24" t="n"/>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.8100 (aec-wnba-tor-dal-2026-08-12); model edge vs ask -0.0578. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG27" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH27" s="24" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="n"/>
+      <c r="AK27" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN27" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP27" s="24" t="inlineStr">
+        <is>
+          <t>wnba-tor</t>
+        </is>
+      </c>
+      <c r="AQ27" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="AR27" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="AS27" s="24" t="inlineStr">
+        <is>
+          <t>wnba-dal</t>
+        </is>
+      </c>
+      <c r="AT27" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AU27" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AV27" s="24" t="n"/>
+      <c r="AW27" s="24" t="n"/>
+      <c r="AX27" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY27" s="24" t="n"/>
+      <c r="AZ27" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB27" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE27" s="24" t="inlineStr">
+        <is>
+          <t>bed262b4cc2cb026</t>
+        </is>
+      </c>
+      <c r="BF27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG27" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:41:29.908829Z</t>
+        </is>
+      </c>
+      <c r="BI27" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ27" s="25" t="n"/>
+      <c r="BK27" s="26" t="n">
+        <v>-426</v>
+      </c>
+      <c r="BL27" s="27" t="n">
+        <v>1.234742</v>
+      </c>
+      <c r="BM27" s="28" t="n">
+        <v>0.809886</v>
+      </c>
+      <c r="BN27" s="28" t="n">
+        <v>0.80198</v>
+      </c>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
+      <c r="BR27" s="28" t="n"/>
+      <c r="BS27" s="28" t="n"/>
+      <c r="BT27" s="28" t="n"/>
+      <c r="BU27" s="25" t="n"/>
+      <c r="BV27" s="29" t="n"/>
+      <c r="BW27" s="24" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
+      <c r="BZ27" s="24" t="n"/>
+      <c r="CA27" s="31" t="n"/>
+      <c r="CB27" s="24" t="n"/>
+      <c r="CC27" s="24" t="inlineStr">
+        <is>
+          <t>0.8593821994</t>
+        </is>
+      </c>
+      <c r="CD27" s="24" t="inlineStr">
+        <is>
+          <t>1.688216</t>
+        </is>
+      </c>
+      <c r="CE27" s="24" t="n"/>
+      <c r="CF27" s="24" t="n"/>
+      <c r="CG27" s="24" t="n"/>
+      <c r="CH27" s="24" t="n"/>
+      <c r="CI27" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ27" s="24" t="inlineStr">
+        <is>
+          <t>0.008501</t>
+        </is>
+      </c>
+      <c r="CK27" s="24" t="n"/>
+      <c r="CL27" s="24" t="n"/>
+      <c r="CM27" s="24" t="n"/>
+      <c r="CN27" s="24" t="n"/>
+      <c r="CO27" s="24" t="n"/>
+      <c r="CP27" s="24" t="n"/>
+      <c r="CQ27" s="24" t="n"/>
+      <c r="CR27" s="24" t="inlineStr">
+        <is>
+          <t>0.752207</t>
+        </is>
+      </c>
+      <c r="CS27" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>0f469055cfd54d3a</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T19:33:32.932123Z</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>401857138</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>-376</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <v>1.265957</v>
+      </c>
+      <c r="N28" s="28" t="n">
+        <v>0.789916</v>
+      </c>
+      <c r="O28" s="28" t="n">
+        <v>0.7756999999999999</v>
+      </c>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="28" t="n">
+        <v>-0.014216</v>
+      </c>
+      <c r="R28" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="S28" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U28" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="n"/>
+      <c r="W28" s="26" t="n"/>
+      <c r="X28" s="26" t="n"/>
+      <c r="Y28" s="25" t="n"/>
+      <c r="Z28" s="26" t="n"/>
+      <c r="AA28" s="28" t="n"/>
+      <c r="AB28" s="28" t="n"/>
+      <c r="AC28" s="30" t="n"/>
+      <c r="AD28" s="24" t="n"/>
+      <c r="AE28" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.7900 (aec-wnba-chi-gsv-2026-08-12); model edge vs ask -0.0143.</t>
+        </is>
+      </c>
+      <c r="AF28" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG28" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH28" s="24" t="n"/>
+      <c r="AI28" s="31" t="n"/>
+      <c r="AJ28" s="31" t="n"/>
+      <c r="AK28" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN28" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP28" s="24" t="inlineStr">
+        <is>
+          <t>wnba-chi</t>
+        </is>
+      </c>
+      <c r="AQ28" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="AR28" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="AS28" s="24" t="inlineStr">
+        <is>
+          <t>wnba-gsv</t>
+        </is>
+      </c>
+      <c r="AT28" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="AU28" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="AV28" s="24" t="n"/>
+      <c r="AW28" s="24" t="n"/>
+      <c r="AX28" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY28" s="24" t="n"/>
+      <c r="AZ28" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA28" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB28" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC28" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD28" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE28" s="24" t="inlineStr">
+        <is>
+          <t>25be967f882f1f6d</t>
+        </is>
+      </c>
+      <c r="BF28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG28" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:41:30.522789Z</t>
+        </is>
+      </c>
+      <c r="BI28" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ28" s="25" t="n"/>
+      <c r="BK28" s="26" t="n">
+        <v>-376</v>
+      </c>
+      <c r="BL28" s="27" t="n">
+        <v>1.265957</v>
+      </c>
+      <c r="BM28" s="28" t="n">
+        <v>0.789916</v>
+      </c>
+      <c r="BN28" s="28" t="n">
+        <v>0.782178</v>
+      </c>
+      <c r="BO28" s="28" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n"/>
+      <c r="BR28" s="28" t="n"/>
+      <c r="BS28" s="28" t="n"/>
+      <c r="BT28" s="28" t="n"/>
+      <c r="BU28" s="25" t="n"/>
+      <c r="BV28" s="29" t="n"/>
+      <c r="BW28" s="24" t="n"/>
+      <c r="BX28" s="30" t="n"/>
+      <c r="BY28" s="27" t="n"/>
+      <c r="BZ28" s="24" t="n"/>
+      <c r="CA28" s="31" t="n"/>
+      <c r="CB28" s="24" t="n"/>
+      <c r="CC28" s="24" t="inlineStr">
+        <is>
+          <t>0.8909512632</t>
+        </is>
+      </c>
+      <c r="CD28" s="24" t="inlineStr">
+        <is>
+          <t>-3.866065</t>
+        </is>
+      </c>
+      <c r="CE28" s="24" t="n"/>
+      <c r="CF28" s="24" t="n"/>
+      <c r="CG28" s="24" t="n"/>
+      <c r="CH28" s="24" t="n"/>
+      <c r="CI28" s="24" t="n"/>
+      <c r="CJ28" s="24" t="inlineStr">
+        <is>
+          <t>2.087162</t>
+        </is>
+      </c>
+      <c r="CK28" s="24" t="n"/>
+      <c r="CL28" s="24" t="n"/>
+      <c r="CM28" s="24" t="n"/>
+      <c r="CN28" s="24" t="n"/>
+      <c r="CO28" s="24" t="n"/>
+      <c r="CP28" s="24" t="n"/>
+      <c r="CQ28" s="24" t="n"/>
+      <c r="CR28" s="24" t="inlineStr">
+        <is>
+          <t>0.7757</t>
+        </is>
+      </c>
+      <c r="CS28" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>4f440b62ebff4d85</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T19:33:32.932123Z</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>401857139</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>-733</v>
+      </c>
+      <c r="M29" s="27" t="n">
+        <v>1.136426</v>
+      </c>
+      <c r="N29" s="28" t="n">
+        <v>0.879952</v>
+      </c>
+      <c r="O29" s="28" t="n">
+        <v>0.723101</v>
+      </c>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="28" t="n">
+        <v>-0.156851</v>
+      </c>
+      <c r="R29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U29" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="n"/>
+      <c r="W29" s="26" t="n"/>
+      <c r="X29" s="26" t="n"/>
+      <c r="Y29" s="25" t="n"/>
+      <c r="Z29" s="26" t="n"/>
+      <c r="AA29" s="28" t="n"/>
+      <c r="AB29" s="28" t="n"/>
+      <c r="AC29" s="30" t="n"/>
+      <c r="AD29" s="24" t="n"/>
+      <c r="AE29" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.8800 (aec-wnba-min-por-2026-08-12); model edge vs ask -0.1569. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF29" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG29" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH29" s="24" t="n"/>
+      <c r="AI29" s="31" t="n"/>
+      <c r="AJ29" s="31" t="n"/>
+      <c r="AK29" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL29" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN29" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP29" s="24" t="inlineStr">
+        <is>
+          <t>wnba-min</t>
+        </is>
+      </c>
+      <c r="AQ29" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="AR29" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="AS29" s="24" t="inlineStr">
+        <is>
+          <t>wnba-por</t>
+        </is>
+      </c>
+      <c r="AT29" s="24" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="AU29" s="24" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="AV29" s="24" t="n"/>
+      <c r="AW29" s="24" t="n"/>
+      <c r="AX29" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY29" s="24" t="n"/>
+      <c r="AZ29" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA29" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB29" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC29" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD29" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE29" s="24" t="inlineStr">
+        <is>
+          <t>54b300fef3816245</t>
+        </is>
+      </c>
+      <c r="BF29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG29" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:41:30.941772Z</t>
+        </is>
+      </c>
+      <c r="BI29" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ29" s="25" t="n"/>
+      <c r="BK29" s="26" t="n">
+        <v>-733</v>
+      </c>
+      <c r="BL29" s="27" t="n">
+        <v>1.136426</v>
+      </c>
+      <c r="BM29" s="28" t="n">
+        <v>0.879952</v>
+      </c>
+      <c r="BN29" s="28" t="n">
+        <v>0.871287</v>
+      </c>
+      <c r="BO29" s="28" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
+      <c r="BR29" s="28" t="n"/>
+      <c r="BS29" s="28" t="n"/>
+      <c r="BT29" s="28" t="n"/>
+      <c r="BU29" s="25" t="n"/>
+      <c r="BV29" s="29" t="n"/>
+      <c r="BW29" s="24" t="n"/>
+      <c r="BX29" s="30" t="n"/>
+      <c r="BY29" s="27" t="n"/>
+      <c r="BZ29" s="24" t="n"/>
+      <c r="CA29" s="31" t="n"/>
+      <c r="CB29" s="24" t="n"/>
+      <c r="CC29" s="24" t="inlineStr">
+        <is>
+          <t>0.1965379833</t>
+        </is>
+      </c>
+      <c r="CD29" s="24" t="inlineStr">
+        <is>
+          <t>-1.095212</t>
+        </is>
+      </c>
+      <c r="CE29" s="24" t="n"/>
+      <c r="CF29" s="24" t="n"/>
+      <c r="CG29" s="24" t="n"/>
+      <c r="CH29" s="24" t="n"/>
+      <c r="CI29" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ29" s="24" t="inlineStr">
+        <is>
+          <t>3.932321</t>
+        </is>
+      </c>
+      <c r="CK29" s="24" t="n"/>
+      <c r="CL29" s="24" t="n"/>
+      <c r="CM29" s="24" t="n"/>
+      <c r="CN29" s="24" t="n"/>
+      <c r="CO29" s="24" t="n"/>
+      <c r="CP29" s="24" t="n"/>
+      <c r="CQ29" s="24" t="n"/>
+      <c r="CR29" s="24" t="inlineStr">
+        <is>
+          <t>0.723101</t>
+        </is>
+      </c>
+      <c r="CS29" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/main/wnba.xlsx
+++ b/data/main/wnba.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS29" headerRowCount="1">
-  <autoFilter ref="A1:CS29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS32" headerRowCount="1">
+  <autoFilter ref="A1:CS32"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$29)</f>
+        <f>COUNTA('Picks'!$A$2:$A$32)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$29,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$32,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$32,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$32,"settled",'Picks'!$V$2:$V$32,"win")+COUNTIFS('Picks'!$U$2:$U$32,"settled",'Picks'!$V$2:$V$32,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$29,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$32,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$32,"&gt;0",'Picks'!$V$2:$V$32,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$32,"&gt;0",'Picks'!$V$2:$V$32,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")/(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$32,"&gt;0",'Picks'!$V$2:$V$32,"win")/(COUNTIFS('Picks'!$BX$2:$BX$32,"&gt;0",'Picks'!$V$2:$V$32,"win")+COUNTIFS('Picks'!$BX$2:$BX$32,"&gt;0",'Picks'!$V$2:$V$32,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$29)/SUM('Picks'!$BX$2:$BX$29),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$32)/SUM('Picks'!$BX$2:$BX$32),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$29)</f>
+        <f>SUM('Picks'!$BY$2:$BY$32)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$29,"&lt;&gt;",'Picks'!$AB$2:$AB$29),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$32,"&lt;&gt;",'Picks'!$AB$2:$AB$32),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$32,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$32,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$29,'Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$32,'Picks'!$AM$2:$AM$32,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$32,$A14,'Picks'!$U$2:$U$32,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$32,$A14,'Picks'!$U$2:$U$32,"settled",'Picks'!$V$2:$V$32,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$32,$A14,'Picks'!$U$2:$U$32,"settled",'Picks'!$V$2:$V$32,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$32,'Picks'!$H$2:$H$32,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$32,'Picks'!$H$2:$H$32,$A14,'Picks'!$U$2:$U$32,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$32,$A15,'Picks'!$U$2:$U$32,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$32,$A15,'Picks'!$U$2:$U$32,"settled",'Picks'!$V$2:$V$32,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$32,$A15,'Picks'!$U$2:$U$32,"settled",'Picks'!$V$2:$V$32,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$32,'Picks'!$H$2:$H$32,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$32,'Picks'!$H$2:$H$32,$A15,'Picks'!$U$2:$U$32,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$32,$A16,'Picks'!$U$2:$U$32,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$32,$A16,'Picks'!$U$2:$U$32,"settled",'Picks'!$V$2:$V$32,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$32,$A16,'Picks'!$U$2:$U$32,"settled",'Picks'!$V$2:$V$32,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$32,'Picks'!$H$2:$H$32,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$32,'Picks'!$H$2:$H$32,$A16,'Picks'!$U$2:$U$32,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS29"/>
+  <dimension ref="A1:CS32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8519,18 +8519,32 @@
       </c>
       <c r="U25" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V25" s="24" t="n"/>
-      <c r="W25" s="26" t="n"/>
-      <c r="X25" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W25" s="26" t="n">
+        <v>95</v>
+      </c>
+      <c r="X25" s="26" t="n">
+        <v>107</v>
+      </c>
       <c r="Y25" s="25" t="n"/>
       <c r="Z25" s="26" t="n"/>
       <c r="AA25" s="28" t="n"/>
       <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n"/>
-      <c r="AD25" s="24" t="n"/>
+      <c r="AC25" s="30" t="n">
+        <v>0.2729</v>
+      </c>
+      <c r="AD25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:13:36.678663Z</t>
+        </is>
+      </c>
       <c r="AE25" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5001; executable ask 0.8800 (aec-wnba-tor-atl-2026-08-10); model edge vs ask -0.1429. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
@@ -8810,18 +8824,32 @@
       </c>
       <c r="U26" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V26" s="24" t="n"/>
-      <c r="W26" s="26" t="n"/>
-      <c r="X26" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W26" s="26" t="n">
+        <v>88</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <v>97</v>
+      </c>
       <c r="Y26" s="25" t="n"/>
       <c r="Z26" s="26" t="n"/>
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n"/>
-      <c r="AD26" s="24" t="n"/>
+      <c r="AC26" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:13:36.979390Z</t>
+        </is>
+      </c>
       <c r="AE26" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5001; executable ask 0.5300 (aec-wnba-chi-sea-2026-08-10); model edge vs ask +0.0132.</t>
@@ -8834,7 +8862,7 @@
       </c>
       <c r="AG26" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH26" s="24" t="n"/>
@@ -9019,12 +9047,12 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>9397e6d8aee7453d</t>
+          <t>861a886108cf403d</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T19:33:32.932123Z</t>
+          <t>2026-08-12T21:16:50.725033Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -9097,18 +9125,32 @@
       </c>
       <c r="U27" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V27" s="24" t="n"/>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W27" s="26" t="n">
+        <v>88</v>
+      </c>
+      <c r="X27" s="26" t="n">
+        <v>94</v>
+      </c>
       <c r="Y27" s="25" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n"/>
-      <c r="AD27" s="24" t="n"/>
+      <c r="AC27" s="30" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="AD27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:31:01.137054Z</t>
+        </is>
+      </c>
       <c r="AE27" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5001; executable ask 0.8100 (aec-wnba-tor-dal-2026-08-12); model edge vs ask -0.0578. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
@@ -9230,7 +9272,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:41:29.908829Z</t>
+          <t>2026-08-12T21:16:26.173511Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -9310,12 +9352,12 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>0f469055cfd54d3a</t>
+          <t>72137c22563b4746</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T19:33:32.932123Z</t>
+          <t>2026-08-12T21:16:50.725033Z</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
@@ -9388,18 +9430,32 @@
       </c>
       <c r="U28" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V28" s="24" t="n"/>
-      <c r="W28" s="26" t="n"/>
-      <c r="X28" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W28" s="26" t="n">
+        <v>71</v>
+      </c>
+      <c r="X28" s="26" t="n">
+        <v>91</v>
+      </c>
       <c r="Y28" s="25" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="30" t="n"/>
-      <c r="AD28" s="24" t="n"/>
+      <c r="AC28" s="30" t="n">
+        <v>0.5319</v>
+      </c>
+      <c r="AD28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:31:01.522228Z</t>
+        </is>
+      </c>
       <c r="AE28" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5001; executable ask 0.7900 (aec-wnba-chi-gsv-2026-08-12); model edge vs ask -0.0143.</t>
@@ -9521,7 +9577,7 @@
       </c>
       <c r="BH28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:41:30.522789Z</t>
+          <t>2026-08-12T21:16:26.781920Z</t>
         </is>
       </c>
       <c r="BI28" s="24" t="inlineStr">
@@ -9597,12 +9653,12 @@
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>4f440b62ebff4d85</t>
+          <t>e8731de8bd364854</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T19:33:32.932123Z</t>
+          <t>2026-08-12T21:16:50.725033Z</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -9647,20 +9703,20 @@
         </is>
       </c>
       <c r="L29" s="26" t="n">
-        <v>-733</v>
+        <v>-614</v>
       </c>
       <c r="M29" s="27" t="n">
-        <v>1.136426</v>
+        <v>1.162866</v>
       </c>
       <c r="N29" s="28" t="n">
-        <v>0.879952</v>
+        <v>0.859944</v>
       </c>
       <c r="O29" s="28" t="n">
         <v>0.723101</v>
       </c>
       <c r="P29" s="28" t="n"/>
       <c r="Q29" s="28" t="n">
-        <v>-0.156851</v>
+        <v>-0.136843</v>
       </c>
       <c r="R29" s="26" t="n">
         <v>0</v>
@@ -9675,21 +9731,35 @@
       </c>
       <c r="U29" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V29" s="24" t="n"/>
-      <c r="W29" s="26" t="n"/>
-      <c r="X29" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W29" s="26" t="n">
+        <v>85</v>
+      </c>
+      <c r="X29" s="26" t="n">
+        <v>81</v>
+      </c>
       <c r="Y29" s="25" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="30" t="n"/>
-      <c r="AD29" s="24" t="n"/>
+      <c r="AC29" s="30" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="AD29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:31:01.898406Z</t>
+        </is>
+      </c>
       <c r="AE29" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.8800 (aec-wnba-min-por-2026-08-12); model edge vs ask -0.1569. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.8600 (aec-wnba-min-por-2026-08-12); model edge vs ask -0.1369. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
         </is>
       </c>
       <c r="AF29" s="31" t="inlineStr">
@@ -9808,7 +9878,7 @@
       </c>
       <c r="BH29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:41:30.941772Z</t>
+          <t>2026-08-12T21:16:27.215401Z</t>
         </is>
       </c>
       <c r="BI29" s="24" t="inlineStr">
@@ -9818,16 +9888,16 @@
       </c>
       <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
-        <v>-733</v>
+        <v>-614</v>
       </c>
       <c r="BL29" s="27" t="n">
-        <v>1.136426</v>
+        <v>1.162866</v>
       </c>
       <c r="BM29" s="28" t="n">
-        <v>0.879952</v>
+        <v>0.859944</v>
       </c>
       <c r="BN29" s="28" t="n">
-        <v>0.871287</v>
+        <v>0.851485</v>
       </c>
       <c r="BO29" s="28" t="n"/>
       <c r="BP29" s="25" t="n"/>
@@ -9885,6 +9955,871 @@
         </is>
       </c>
     </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>69af92096efc415b</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:14:51.037990Z</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>401857140</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>Connecticut Sun</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>-456</v>
+      </c>
+      <c r="M30" s="27" t="n">
+        <v>1.219298</v>
+      </c>
+      <c r="N30" s="28" t="n">
+        <v>0.820144</v>
+      </c>
+      <c r="O30" s="28" t="n">
+        <v>0.6314380000000001</v>
+      </c>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="28" t="n">
+        <v>-0.188706</v>
+      </c>
+      <c r="R30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T30" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U30" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="n"/>
+      <c r="W30" s="26" t="n"/>
+      <c r="X30" s="26" t="n"/>
+      <c r="Y30" s="25" t="n"/>
+      <c r="Z30" s="26" t="n"/>
+      <c r="AA30" s="28" t="n"/>
+      <c r="AB30" s="28" t="n"/>
+      <c r="AC30" s="30" t="n"/>
+      <c r="AD30" s="24" t="n"/>
+      <c r="AE30" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.8200 (aec-wnba-atl-conn-2026-08-13); model edge vs ask -0.1886. NOTE: NO_CALL_AVAILABILITY_PLAYER_UNMAPPED unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF30" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG30" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH30" s="24" t="n"/>
+      <c r="AI30" s="31" t="n"/>
+      <c r="AJ30" s="31" t="n"/>
+      <c r="AK30" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL30" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM30" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN30" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO30" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP30" s="24" t="inlineStr">
+        <is>
+          <t>wnba-atl</t>
+        </is>
+      </c>
+      <c r="AQ30" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="AR30" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="AS30" s="24" t="inlineStr">
+        <is>
+          <t>wnba-con</t>
+        </is>
+      </c>
+      <c r="AT30" s="24" t="inlineStr">
+        <is>
+          <t>Connecticut Sun</t>
+        </is>
+      </c>
+      <c r="AU30" s="24" t="inlineStr">
+        <is>
+          <t>Connecticut Sun</t>
+        </is>
+      </c>
+      <c r="AV30" s="24" t="n"/>
+      <c r="AW30" s="24" t="n"/>
+      <c r="AX30" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY30" s="24" t="n"/>
+      <c r="AZ30" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA30" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB30" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC30" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD30" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE30" s="24" t="inlineStr">
+        <is>
+          <t>eb693c1f8106b97c</t>
+        </is>
+      </c>
+      <c r="BF30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG30" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:45.049604Z</t>
+        </is>
+      </c>
+      <c r="BI30" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ30" s="25" t="n"/>
+      <c r="BK30" s="26" t="n">
+        <v>-456</v>
+      </c>
+      <c r="BL30" s="27" t="n">
+        <v>1.219298</v>
+      </c>
+      <c r="BM30" s="28" t="n">
+        <v>0.820144</v>
+      </c>
+      <c r="BN30" s="28" t="n">
+        <v>0.811881</v>
+      </c>
+      <c r="BO30" s="28" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
+      <c r="BR30" s="28" t="n"/>
+      <c r="BS30" s="28" t="n"/>
+      <c r="BT30" s="28" t="n"/>
+      <c r="BU30" s="25" t="n"/>
+      <c r="BV30" s="29" t="n"/>
+      <c r="BW30" s="24" t="n"/>
+      <c r="BX30" s="30" t="n"/>
+      <c r="BY30" s="27" t="n"/>
+      <c r="BZ30" s="24" t="n"/>
+      <c r="CA30" s="31" t="n"/>
+      <c r="CB30" s="24" t="n"/>
+      <c r="CC30" s="24" t="inlineStr">
+        <is>
+          <t>0.3258499922</t>
+        </is>
+      </c>
+      <c r="CD30" s="24" t="inlineStr">
+        <is>
+          <t>-4.55436</t>
+        </is>
+      </c>
+      <c r="CE30" s="24" t="n"/>
+      <c r="CF30" s="24" t="n"/>
+      <c r="CG30" s="24" t="n"/>
+      <c r="CH30" s="24" t="n"/>
+      <c r="CI30" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_PLAYER_UNMAPPED</t>
+        </is>
+      </c>
+      <c r="CJ30" s="24" t="inlineStr">
+        <is>
+          <t>6.374313</t>
+        </is>
+      </c>
+      <c r="CK30" s="24" t="n"/>
+      <c r="CL30" s="24" t="n"/>
+      <c r="CM30" s="24" t="n"/>
+      <c r="CN30" s="24" t="n"/>
+      <c r="CO30" s="24" t="n"/>
+      <c r="CP30" s="24" t="n"/>
+      <c r="CQ30" s="24" t="n"/>
+      <c r="CR30" s="24" t="inlineStr">
+        <is>
+          <t>0.631438</t>
+        </is>
+      </c>
+      <c r="CS30" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>ea1766b2eb704999</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:14:51.037990Z</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T20:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>401857141</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>-355</v>
+      </c>
+      <c r="M31" s="27" t="n">
+        <v>1.28169</v>
+      </c>
+      <c r="N31" s="28" t="n">
+        <v>0.78022</v>
+      </c>
+      <c r="O31" s="28" t="n">
+        <v>0.70842</v>
+      </c>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="28" t="n">
+        <v>-0.0718</v>
+      </c>
+      <c r="R31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U31" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="n"/>
+      <c r="W31" s="26" t="n"/>
+      <c r="X31" s="26" t="n"/>
+      <c r="Y31" s="25" t="n"/>
+      <c r="Z31" s="26" t="n"/>
+      <c r="AA31" s="28" t="n"/>
+      <c r="AB31" s="28" t="n"/>
+      <c r="AC31" s="30" t="n"/>
+      <c r="AD31" s="24" t="n"/>
+      <c r="AE31" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.7800 (aec-wnba-la-ny-2026-08-13); model edge vs ask -0.0716.</t>
+        </is>
+      </c>
+      <c r="AF31" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG31" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH31" s="24" t="n"/>
+      <c r="AI31" s="31" t="n"/>
+      <c r="AJ31" s="31" t="n"/>
+      <c r="AK31" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL31" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM31" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN31" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO31" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP31" s="24" t="inlineStr">
+        <is>
+          <t>wnba-las</t>
+        </is>
+      </c>
+      <c r="AQ31" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AR31" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AS31" s="24" t="inlineStr">
+        <is>
+          <t>wnba-nyl</t>
+        </is>
+      </c>
+      <c r="AT31" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AU31" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AV31" s="24" t="n"/>
+      <c r="AW31" s="24" t="n"/>
+      <c r="AX31" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY31" s="24" t="n"/>
+      <c r="AZ31" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA31" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB31" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC31" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD31" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE31" s="24" t="inlineStr">
+        <is>
+          <t>16b7a00d19006dde</t>
+        </is>
+      </c>
+      <c r="BF31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG31" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:45.988570Z</t>
+        </is>
+      </c>
+      <c r="BI31" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ31" s="25" t="n"/>
+      <c r="BK31" s="26" t="n">
+        <v>-355</v>
+      </c>
+      <c r="BL31" s="27" t="n">
+        <v>1.28169</v>
+      </c>
+      <c r="BM31" s="28" t="n">
+        <v>0.78022</v>
+      </c>
+      <c r="BN31" s="28" t="n">
+        <v>0.772277</v>
+      </c>
+      <c r="BO31" s="28" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n"/>
+      <c r="BR31" s="28" t="n"/>
+      <c r="BS31" s="28" t="n"/>
+      <c r="BT31" s="28" t="n"/>
+      <c r="BU31" s="25" t="n"/>
+      <c r="BV31" s="29" t="n"/>
+      <c r="BW31" s="24" t="n"/>
+      <c r="BX31" s="30" t="n"/>
+      <c r="BY31" s="27" t="n"/>
+      <c r="BZ31" s="24" t="n"/>
+      <c r="CA31" s="31" t="n"/>
+      <c r="CB31" s="24" t="n"/>
+      <c r="CC31" s="24" t="inlineStr">
+        <is>
+          <t>0.7947999616</t>
+        </is>
+      </c>
+      <c r="CD31" s="24" t="inlineStr">
+        <is>
+          <t>5.744366</t>
+        </is>
+      </c>
+      <c r="CE31" s="24" t="n"/>
+      <c r="CF31" s="24" t="n"/>
+      <c r="CG31" s="24" t="n"/>
+      <c r="CH31" s="24" t="n"/>
+      <c r="CI31" s="24" t="n"/>
+      <c r="CJ31" s="24" t="inlineStr">
+        <is>
+          <t>-2.420027</t>
+        </is>
+      </c>
+      <c r="CK31" s="24" t="n"/>
+      <c r="CL31" s="24" t="n"/>
+      <c r="CM31" s="24" t="n"/>
+      <c r="CN31" s="24" t="n"/>
+      <c r="CO31" s="24" t="n"/>
+      <c r="CP31" s="24" t="n"/>
+      <c r="CQ31" s="24" t="n"/>
+      <c r="CR31" s="24" t="inlineStr">
+        <is>
+          <t>0.70842</t>
+        </is>
+      </c>
+      <c r="CS31" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>7a00878e4a2f4703</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:14:51.037990Z</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>401857142</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N32" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O32" s="28" t="n">
+        <v>0.637269</v>
+      </c>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="28" t="n">
+        <v>-0.032698</v>
+      </c>
+      <c r="R32" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="S32" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T32" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U32" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="n"/>
+      <c r="W32" s="26" t="n"/>
+      <c r="X32" s="26" t="n"/>
+      <c r="Y32" s="25" t="n"/>
+      <c r="Z32" s="26" t="n"/>
+      <c r="AA32" s="28" t="n"/>
+      <c r="AB32" s="28" t="n"/>
+      <c r="AC32" s="30" t="n"/>
+      <c r="AD32" s="24" t="n"/>
+      <c r="AE32" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.6700 (aec-wnba-wsh-lv-2026-08-13); model edge vs ask -0.0327.</t>
+        </is>
+      </c>
+      <c r="AF32" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG32" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH32" s="24" t="n"/>
+      <c r="AI32" s="31" t="n"/>
+      <c r="AJ32" s="31" t="n"/>
+      <c r="AK32" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN32" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP32" s="24" t="inlineStr">
+        <is>
+          <t>wnba-was</t>
+        </is>
+      </c>
+      <c r="AQ32" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AR32" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AS32" s="24" t="inlineStr">
+        <is>
+          <t>wnba-lva</t>
+        </is>
+      </c>
+      <c r="AT32" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="AU32" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="AV32" s="24" t="n"/>
+      <c r="AW32" s="24" t="n"/>
+      <c r="AX32" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY32" s="24" t="n"/>
+      <c r="AZ32" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA32" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB32" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC32" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD32" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE32" s="24" t="inlineStr">
+        <is>
+          <t>ff96e0111a58886e</t>
+        </is>
+      </c>
+      <c r="BF32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG32" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:46.550249Z</t>
+        </is>
+      </c>
+      <c r="BI32" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ32" s="25" t="n"/>
+      <c r="BK32" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL32" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM32" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN32" s="28" t="n">
+        <v>0.663366</v>
+      </c>
+      <c r="BO32" s="28" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n"/>
+      <c r="BR32" s="28" t="n"/>
+      <c r="BS32" s="28" t="n"/>
+      <c r="BT32" s="28" t="n"/>
+      <c r="BU32" s="25" t="n"/>
+      <c r="BV32" s="29" t="n"/>
+      <c r="BW32" s="24" t="n"/>
+      <c r="BX32" s="30" t="n"/>
+      <c r="BY32" s="27" t="n"/>
+      <c r="BZ32" s="24" t="n"/>
+      <c r="CA32" s="31" t="n"/>
+      <c r="CB32" s="24" t="n"/>
+      <c r="CC32" s="24" t="inlineStr">
+        <is>
+          <t>0.6691278675</t>
+        </is>
+      </c>
+      <c r="CD32" s="24" t="inlineStr">
+        <is>
+          <t>-3.282439</t>
+        </is>
+      </c>
+      <c r="CE32" s="24" t="n"/>
+      <c r="CF32" s="24" t="n"/>
+      <c r="CG32" s="24" t="n"/>
+      <c r="CH32" s="24" t="n"/>
+      <c r="CI32" s="24" t="n"/>
+      <c r="CJ32" s="24" t="inlineStr">
+        <is>
+          <t>-5.390663</t>
+        </is>
+      </c>
+      <c r="CK32" s="24" t="n"/>
+      <c r="CL32" s="24" t="n"/>
+      <c r="CM32" s="24" t="n"/>
+      <c r="CN32" s="24" t="n"/>
+      <c r="CO32" s="24" t="n"/>
+      <c r="CP32" s="24" t="n"/>
+      <c r="CQ32" s="24" t="n"/>
+      <c r="CR32" s="24" t="inlineStr">
+        <is>
+          <t>0.637269</t>
+        </is>
+      </c>
+      <c r="CS32" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
